--- a/data/stats/supp_tables/spweedcounts-anova.xlsx
+++ b/data/stats/supp_tables/spweedcounts-anova.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,11 @@
           <t>p.value</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>p.val_highlight</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -409,6 +414,11 @@
       <c r="F2">
         <v>1.334700324980654E-61</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -433,6 +443,11 @@
       <c r="F3">
         <v>1.476273755918658E-35</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -457,6 +472,11 @@
       <c r="F4">
         <v>0.0410552908621509</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -481,6 +501,11 @@
       <c r="F5">
         <v>4.630589650149915E-11</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -505,6 +530,11 @@
       <c r="F6">
         <v>1.981832927508168E-22</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -529,6 +559,11 @@
       <c r="F7">
         <v>0.0003650762972876766</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,6 +588,11 @@
       <c r="F8">
         <v>0.004260221252228402</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -577,6 +617,11 @@
       <c r="F9">
         <v>0.4369325140339401</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -601,6 +646,11 @@
       <c r="F10">
         <v>3.037081260462201E-10</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -625,6 +675,11 @@
       <c r="F11">
         <v>0.123178465444021</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -649,6 +704,11 @@
       <c r="F12">
         <v>0.06114010449052382</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -673,6 +733,11 @@
       <c r="F13">
         <v>0.0003092116280713259</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SIG</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -697,6 +762,11 @@
       <c r="F14">
         <v>0.4786238629616003</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -721,6 +791,11 @@
       <c r="F15">
         <v>0.562705701370191</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,6 +819,11 @@
       </c>
       <c r="F16">
         <v>0.2612457964110391</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
     </row>
   </sheetData>
